--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -4155,7 +4155,7 @@
         <v>119994160</v>
       </c>
       <c r="B32" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4280,6 +4280,4219 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120487289</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>424</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>694955</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6361282</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120487293</v>
+      </c>
+      <c r="B34" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>694983</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6361234</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120488905</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>695053</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6361117</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120487048</v>
+      </c>
+      <c r="B36" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>449</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>694999</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6361192</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120487290</v>
+      </c>
+      <c r="B37" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>424</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>694944</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6361275</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120487295</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695000</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6361151</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120487054</v>
+      </c>
+      <c r="B39" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>694999</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6361192</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120488067</v>
+      </c>
+      <c r="B40" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>694971</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6361169</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120488893</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>695054</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6361115</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120488904</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>695053</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6361123</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120487277</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>695004</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6361020</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120488903</v>
+      </c>
+      <c r="B44" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>694945</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6361208</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120487046</v>
+      </c>
+      <c r="B45" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>695003</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6361187</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120487041</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>694996</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6361187</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120488053</v>
+      </c>
+      <c r="B47" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>694983</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6361108</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120487049</v>
+      </c>
+      <c r="B48" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>449</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>694996</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6361187</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120487294</v>
+      </c>
+      <c r="B49" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>424</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>694937</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6361266</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120487363</v>
+      </c>
+      <c r="B50" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>694940</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6361207</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120487393</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>694975</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6361311</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120487394</v>
+      </c>
+      <c r="B52" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>694944</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6361275</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120487275</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91272</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>695063</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6361118</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120487060</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>424</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>694955</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6361273</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120487395</v>
+      </c>
+      <c r="B55" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>694976</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6361175</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120484480</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Brajdvät, Brajdvät, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>695044</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6360990</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120487411</v>
+      </c>
+      <c r="B57" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>694968</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6361174</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120487043</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97952</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>694999</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6361192</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120487292</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>424</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>694942</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6361278</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>många fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120487332</v>
+      </c>
+      <c r="B60" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>694975</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6361311</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120487034</v>
+      </c>
+      <c r="B61" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>695029</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6361151</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120488897</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>424</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>695068</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6361100</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120488051</v>
+      </c>
+      <c r="B63" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>694954</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6361151</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120488049</v>
+      </c>
+      <c r="B64" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>694943</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6361165</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120487412</v>
+      </c>
+      <c r="B65" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>695014</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6361123</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120488894</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>695063</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6361108</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120487031</v>
+      </c>
+      <c r="B67" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>694945</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6361314</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120488064</v>
+      </c>
+      <c r="B68" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>695059</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6361135</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120488052</v>
+      </c>
+      <c r="B69" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Klinte2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>694976</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6361129</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120487032</v>
+      </c>
+      <c r="B70" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>695026</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6361133</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120487059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>424</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mulde-Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>694945</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6361277</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487293</v>
+        <v>120487290</v>
       </c>
       <c r="B34" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4400,38 +4400,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>694983</v>
+        <v>694944</v>
       </c>
       <c r="R34" t="n">
-        <v>6361234</v>
+        <v>6361275</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,12 +4478,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4609,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120487048</v>
+        <v>120488893</v>
       </c>
       <c r="B36" t="n">
-        <v>86367</v>
+        <v>90356</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4625,37 +4625,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449</v>
+        <v>2015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>694999</v>
+        <v>695054</v>
       </c>
       <c r="R36" t="n">
-        <v>6361192</v>
+        <v>6361115</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4699,12 +4708,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4715,10 +4724,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487290</v>
+        <v>120487393</v>
       </c>
       <c r="B37" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4727,25 +4736,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4755,10 +4764,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>694944</v>
+        <v>694975</v>
       </c>
       <c r="R37" t="n">
-        <v>6361275</v>
+        <v>6361311</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4821,7 +4830,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120487295</v>
+        <v>120487277</v>
       </c>
       <c r="B38" t="n">
         <v>86282</v>
@@ -4861,10 +4870,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695000</v>
+        <v>695004</v>
       </c>
       <c r="R38" t="n">
-        <v>6361151</v>
+        <v>6361020</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4927,10 +4936,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120487054</v>
+        <v>120488903</v>
       </c>
       <c r="B39" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4939,41 +4948,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>694999</v>
+        <v>694945</v>
       </c>
       <c r="R39" t="n">
-        <v>6361192</v>
+        <v>6361208</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5017,12 +5035,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5033,10 +5051,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120488067</v>
+        <v>120487032</v>
       </c>
       <c r="B40" t="n">
-        <v>86414</v>
+        <v>86465</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5045,38 +5063,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>694971</v>
+        <v>695026</v>
       </c>
       <c r="R40" t="n">
-        <v>6361169</v>
+        <v>6361133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,12 +5141,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5139,10 +5157,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120488893</v>
+        <v>120487049</v>
       </c>
       <c r="B41" t="n">
-        <v>90356</v>
+        <v>86367</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5155,46 +5173,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695054</v>
+        <v>694996</v>
       </c>
       <c r="R41" t="n">
-        <v>6361115</v>
+        <v>6361187</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5238,12 +5247,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5254,10 +5263,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120488904</v>
+        <v>120487395</v>
       </c>
       <c r="B42" t="n">
-        <v>86373</v>
+        <v>86282</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5266,50 +5275,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695053</v>
+        <v>694976</v>
       </c>
       <c r="R42" t="n">
-        <v>6361123</v>
+        <v>6361175</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5353,12 +5353,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5369,7 +5369,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487277</v>
+        <v>120487034</v>
       </c>
       <c r="B43" t="n">
         <v>86282</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695004</v>
+        <v>695029</v>
       </c>
       <c r="R43" t="n">
-        <v>6361020</v>
+        <v>6361151</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5475,10 +5475,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120488903</v>
+        <v>120487275</v>
       </c>
       <c r="B44" t="n">
-        <v>86373</v>
+        <v>91272</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5487,50 +5487,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>248956</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>694945</v>
+        <v>695063</v>
       </c>
       <c r="R44" t="n">
-        <v>6361208</v>
+        <v>6361118</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5574,12 +5565,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5590,10 +5581,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487046</v>
+        <v>120488053</v>
       </c>
       <c r="B45" t="n">
-        <v>86373</v>
+        <v>86282</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5602,38 +5593,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695003</v>
+        <v>694983</v>
       </c>
       <c r="R45" t="n">
-        <v>6361187</v>
+        <v>6361108</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,25 +5659,29 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5697,10 +5692,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487041</v>
+        <v>120487412</v>
       </c>
       <c r="B46" t="n">
-        <v>86282</v>
+        <v>86414</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5713,34 +5708,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>694996</v>
+        <v>695014</v>
       </c>
       <c r="R46" t="n">
-        <v>6361187</v>
+        <v>6361123</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5787,12 +5782,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5803,7 +5798,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120488053</v>
+        <v>120487041</v>
       </c>
       <c r="B47" t="n">
         <v>86282</v>
@@ -5839,14 +5834,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>694983</v>
+        <v>694996</v>
       </c>
       <c r="R47" t="n">
-        <v>6361108</v>
+        <v>6361187</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5881,11 +5876,6 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5898,12 +5888,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5914,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487049</v>
+        <v>120487294</v>
       </c>
       <c r="B48" t="n">
-        <v>86367</v>
+        <v>86302</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5930,34 +5920,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>694996</v>
+        <v>694937</v>
       </c>
       <c r="R48" t="n">
-        <v>6361187</v>
+        <v>6361266</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6004,12 +5994,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6020,10 +6010,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487294</v>
+        <v>120488067</v>
       </c>
       <c r="B49" t="n">
-        <v>86302</v>
+        <v>86414</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6032,38 +6022,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694937</v>
+        <v>694971</v>
       </c>
       <c r="R49" t="n">
-        <v>6361266</v>
+        <v>6361169</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6110,12 +6100,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6126,10 +6116,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487363</v>
+        <v>120487411</v>
       </c>
       <c r="B50" t="n">
-        <v>86373</v>
+        <v>86414</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6138,25 +6128,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6166,10 +6156,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694940</v>
+        <v>694968</v>
       </c>
       <c r="R50" t="n">
-        <v>6361207</v>
+        <v>6361174</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6232,7 +6222,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487393</v>
+        <v>120487394</v>
       </c>
       <c r="B51" t="n">
         <v>86282</v>
@@ -6272,10 +6262,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>694975</v>
+        <v>694944</v>
       </c>
       <c r="R51" t="n">
-        <v>6361311</v>
+        <v>6361275</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6338,7 +6328,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487394</v>
+        <v>120488051</v>
       </c>
       <c r="B52" t="n">
         <v>86282</v>
@@ -6374,14 +6364,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694944</v>
+        <v>694954</v>
       </c>
       <c r="R52" t="n">
-        <v>6361275</v>
+        <v>6361151</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6428,12 +6418,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6444,10 +6434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487275</v>
+        <v>120484480</v>
       </c>
       <c r="B53" t="n">
-        <v>91272</v>
+        <v>90356</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6456,41 +6446,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>2015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Brajdvät, Brajdvät, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695063</v>
+        <v>695044</v>
       </c>
       <c r="R53" t="n">
-        <v>6361118</v>
+        <v>6360990</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6517,29 +6510,40 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6550,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120487060</v>
+        <v>120487043</v>
       </c>
       <c r="B54" t="n">
-        <v>86302</v>
+        <v>97952</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6562,25 +6566,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>424</v>
+        <v>219862</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6590,10 +6594,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694955</v>
+        <v>694999</v>
       </c>
       <c r="R54" t="n">
-        <v>6361273</v>
+        <v>6361192</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6656,10 +6660,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487395</v>
+        <v>120487031</v>
       </c>
       <c r="B55" t="n">
-        <v>86282</v>
+        <v>86465</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6668,38 +6672,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>694976</v>
+        <v>694945</v>
       </c>
       <c r="R55" t="n">
-        <v>6361175</v>
+        <v>6361314</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6746,12 +6750,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6762,10 +6766,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120484480</v>
+        <v>120488064</v>
       </c>
       <c r="B56" t="n">
-        <v>90356</v>
+        <v>86373</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6778,40 +6782,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brajdvät, Brajdvät, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695044</v>
+        <v>695059</v>
       </c>
       <c r="R56" t="n">
-        <v>6360990</v>
+        <v>6361135</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6838,40 +6839,29 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6882,10 +6872,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487411</v>
+        <v>120488052</v>
       </c>
       <c r="B57" t="n">
-        <v>86414</v>
+        <v>86282</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6898,34 +6888,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>694968</v>
+        <v>694976</v>
       </c>
       <c r="R57" t="n">
-        <v>6361174</v>
+        <v>6361129</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6972,12 +6962,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6988,10 +6978,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487043</v>
+        <v>120487292</v>
       </c>
       <c r="B58" t="n">
-        <v>97952</v>
+        <v>86302</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7000,38 +6990,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219862</v>
+        <v>424</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>694999</v>
+        <v>694942</v>
       </c>
       <c r="R58" t="n">
-        <v>6361192</v>
+        <v>6361278</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7066,6 +7056,11 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>många fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7078,12 +7073,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7094,10 +7089,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487292</v>
+        <v>120487295</v>
       </c>
       <c r="B59" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7106,38 +7101,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>694942</v>
+        <v>695000</v>
       </c>
       <c r="R59" t="n">
-        <v>6361278</v>
+        <v>6361151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7172,11 +7167,6 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>många fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7189,12 +7179,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7205,10 +7195,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487332</v>
+        <v>120487054</v>
       </c>
       <c r="B60" t="n">
-        <v>86449</v>
+        <v>100194</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7217,38 +7207,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>694975</v>
+        <v>694999</v>
       </c>
       <c r="R60" t="n">
-        <v>6361311</v>
+        <v>6361192</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7295,12 +7285,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7311,10 +7301,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120487034</v>
+        <v>120488049</v>
       </c>
       <c r="B61" t="n">
-        <v>86282</v>
+        <v>86465</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7323,38 +7313,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>695029</v>
+        <v>694943</v>
       </c>
       <c r="R61" t="n">
-        <v>6361151</v>
+        <v>6361165</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7401,12 +7391,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7417,10 +7407,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120488897</v>
+        <v>120487293</v>
       </c>
       <c r="B62" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7429,50 +7419,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>695068</v>
+        <v>694983</v>
       </c>
       <c r="R62" t="n">
-        <v>6361100</v>
+        <v>6361234</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7516,12 +7497,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7532,10 +7513,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120488051</v>
+        <v>120487059</v>
       </c>
       <c r="B63" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7544,38 +7525,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694954</v>
+        <v>694945</v>
       </c>
       <c r="R63" t="n">
-        <v>6361151</v>
+        <v>6361277</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7622,12 +7603,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7638,10 +7619,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120488049</v>
+        <v>120487060</v>
       </c>
       <c r="B64" t="n">
-        <v>86465</v>
+        <v>86302</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7650,38 +7631,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>694943</v>
+        <v>694955</v>
       </c>
       <c r="R64" t="n">
-        <v>6361165</v>
+        <v>6361273</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7728,12 +7709,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7744,10 +7725,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120487412</v>
+        <v>120487046</v>
       </c>
       <c r="B65" t="n">
-        <v>86414</v>
+        <v>86373</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7756,38 +7737,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695014</v>
+        <v>695003</v>
       </c>
       <c r="R65" t="n">
-        <v>6361123</v>
+        <v>6361187</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7828,18 +7809,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7850,10 +7832,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120488894</v>
+        <v>120487363</v>
       </c>
       <c r="B66" t="n">
-        <v>90356</v>
+        <v>86373</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7866,46 +7848,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>695063</v>
+        <v>694940</v>
       </c>
       <c r="R66" t="n">
-        <v>6361108</v>
+        <v>6361207</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7949,12 +7922,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7965,10 +7938,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120487031</v>
+        <v>120487048</v>
       </c>
       <c r="B67" t="n">
-        <v>86465</v>
+        <v>86367</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7977,25 +7950,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>248947</v>
+        <v>449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8005,10 +7978,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>694945</v>
+        <v>694999</v>
       </c>
       <c r="R67" t="n">
-        <v>6361314</v>
+        <v>6361192</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8071,10 +8044,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120488064</v>
+        <v>120488894</v>
       </c>
       <c r="B68" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8087,37 +8060,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695059</v>
+        <v>695063</v>
       </c>
       <c r="R68" t="n">
-        <v>6361135</v>
+        <v>6361108</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8161,12 +8143,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8177,10 +8159,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120488052</v>
+        <v>120488904</v>
       </c>
       <c r="B69" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8189,41 +8171,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>694976</v>
+        <v>695053</v>
       </c>
       <c r="R69" t="n">
-        <v>6361129</v>
+        <v>6361123</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8267,12 +8258,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8283,10 +8274,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120487032</v>
+        <v>120487332</v>
       </c>
       <c r="B70" t="n">
-        <v>86465</v>
+        <v>86449</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8295,38 +8286,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695026</v>
+        <v>694975</v>
       </c>
       <c r="R70" t="n">
-        <v>6361133</v>
+        <v>6361311</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8373,12 +8364,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8389,7 +8380,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120487059</v>
+        <v>120488897</v>
       </c>
       <c r="B71" t="n">
         <v>86302</v>
@@ -8422,20 +8413,29 @@
           <t>Kalchbr.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>694945</v>
+        <v>695068</v>
       </c>
       <c r="R71" t="n">
-        <v>6361277</v>
+        <v>6361100</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8479,15 +8479,1288 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120505912</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Öst om Däpps, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>694995</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6360841</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120505895</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Öst om Däpps, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>694999</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6360873</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120505911</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Öst om Däpps, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>694994</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6361015</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120504952</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90060</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>694966</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6360945</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120504960</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>694902</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6360953</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120504956</v>
+      </c>
+      <c r="B77" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>695031</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6360930</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120504934</v>
+      </c>
+      <c r="B78" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>695009</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6360998</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120504972</v>
+      </c>
+      <c r="B79" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>694900</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6360951</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120504950</v>
+      </c>
+      <c r="B80" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>449</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>694965</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6360935</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120505913</v>
+      </c>
+      <c r="B81" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Öst om Däpps, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>694996</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6360879</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120504973</v>
+      </c>
+      <c r="B82" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>695009</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6360934</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120504974</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Väst om Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>695028</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6360934</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -4282,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487289</v>
+        <v>120487046</v>
       </c>
       <c r="B33" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4298,34 +4298,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>694955</v>
+        <v>695003</v>
       </c>
       <c r="R33" t="n">
-        <v>6361282</v>
+        <v>6361187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4366,18 +4366,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4388,7 +4389,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487290</v>
+        <v>120487289</v>
       </c>
       <c r="B34" t="n">
         <v>86302</v>
@@ -4428,10 +4429,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>694944</v>
+        <v>694955</v>
       </c>
       <c r="R34" t="n">
-        <v>6361275</v>
+        <v>6361282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4494,7 +4495,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120488905</v>
+        <v>120488064</v>
       </c>
       <c r="B35" t="n">
         <v>86373</v>
@@ -4527,29 +4528,20 @@
           <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695053</v>
+        <v>695059</v>
       </c>
       <c r="R35" t="n">
-        <v>6361117</v>
+        <v>6361135</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4593,12 +4585,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4609,10 +4601,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120488893</v>
+        <v>120487395</v>
       </c>
       <c r="B36" t="n">
-        <v>90356</v>
+        <v>86282</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,50 +4613,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695054</v>
+        <v>694976</v>
       </c>
       <c r="R36" t="n">
-        <v>6361115</v>
+        <v>6361175</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4708,12 +4691,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4724,10 +4707,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487393</v>
+        <v>120487292</v>
       </c>
       <c r="B37" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4736,25 +4719,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4764,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>694975</v>
+        <v>694942</v>
       </c>
       <c r="R37" t="n">
-        <v>6361311</v>
+        <v>6361278</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4800,6 +4783,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>många fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4830,10 +4818,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120487277</v>
+        <v>120487332</v>
       </c>
       <c r="B38" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,38 +4830,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695004</v>
+        <v>694975</v>
       </c>
       <c r="R38" t="n">
-        <v>6361020</v>
+        <v>6361311</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4920,12 +4908,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4936,10 +4924,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120488903</v>
+        <v>120487059</v>
       </c>
       <c r="B39" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4952,46 +4940,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>694945</v>
       </c>
       <c r="R39" t="n">
-        <v>6361208</v>
+        <v>6361277</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5035,12 +5014,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5051,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487032</v>
+        <v>120487048</v>
       </c>
       <c r="B40" t="n">
-        <v>86465</v>
+        <v>86367</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5063,25 +5042,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>248947</v>
+        <v>449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5091,10 +5070,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695026</v>
+        <v>694999</v>
       </c>
       <c r="R40" t="n">
-        <v>6361133</v>
+        <v>6361192</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5157,10 +5136,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487049</v>
+        <v>120487394</v>
       </c>
       <c r="B41" t="n">
-        <v>86367</v>
+        <v>86282</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5169,38 +5148,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694996</v>
+        <v>694944</v>
       </c>
       <c r="R41" t="n">
-        <v>6361187</v>
+        <v>6361275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5247,12 +5226,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5263,10 +5242,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487395</v>
+        <v>120488067</v>
       </c>
       <c r="B42" t="n">
-        <v>86282</v>
+        <v>86414</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5279,34 +5258,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>694976</v>
+        <v>694971</v>
       </c>
       <c r="R42" t="n">
-        <v>6361175</v>
+        <v>6361169</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5353,12 +5332,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5369,10 +5348,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487034</v>
+        <v>120488893</v>
       </c>
       <c r="B43" t="n">
-        <v>86282</v>
+        <v>90356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,41 +5360,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695029</v>
+        <v>695054</v>
       </c>
       <c r="R43" t="n">
-        <v>6361151</v>
+        <v>6361115</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5459,12 +5447,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5475,10 +5463,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487275</v>
+        <v>120488052</v>
       </c>
       <c r="B44" t="n">
-        <v>91272</v>
+        <v>86282</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5491,34 +5479,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>3712</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695063</v>
+        <v>694976</v>
       </c>
       <c r="R44" t="n">
-        <v>6361118</v>
+        <v>6361129</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5565,12 +5553,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5581,10 +5569,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120488053</v>
+        <v>120488049</v>
       </c>
       <c r="B45" t="n">
-        <v>86282</v>
+        <v>86465</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5593,25 +5581,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5621,10 +5609,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>694983</v>
+        <v>694943</v>
       </c>
       <c r="R45" t="n">
-        <v>6361108</v>
+        <v>6361165</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5657,11 +5645,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5692,10 +5675,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487412</v>
+        <v>120487032</v>
       </c>
       <c r="B46" t="n">
-        <v>86414</v>
+        <v>86465</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5704,38 +5687,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695014</v>
+        <v>695026</v>
       </c>
       <c r="R46" t="n">
-        <v>6361123</v>
+        <v>6361133</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5782,12 +5765,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5798,10 +5781,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487041</v>
+        <v>120488905</v>
       </c>
       <c r="B47" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5810,41 +5793,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>694996</v>
+        <v>695053</v>
       </c>
       <c r="R47" t="n">
-        <v>6361187</v>
+        <v>6361117</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5888,12 +5880,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5904,7 +5896,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487294</v>
+        <v>120488897</v>
       </c>
       <c r="B48" t="n">
         <v>86302</v>
@@ -5937,20 +5929,29 @@
           <t>Kalchbr.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>694937</v>
+        <v>695068</v>
       </c>
       <c r="R48" t="n">
-        <v>6361266</v>
+        <v>6361100</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5994,12 +5995,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6010,10 +6011,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120488067</v>
+        <v>120487054</v>
       </c>
       <c r="B49" t="n">
-        <v>86414</v>
+        <v>100194</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6026,34 +6027,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694971</v>
+        <v>694999</v>
       </c>
       <c r="R49" t="n">
-        <v>6361169</v>
+        <v>6361192</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6100,12 +6101,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6116,10 +6117,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487411</v>
+        <v>120487049</v>
       </c>
       <c r="B50" t="n">
-        <v>86414</v>
+        <v>86367</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6128,20 +6129,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6152,14 +6153,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694968</v>
+        <v>694996</v>
       </c>
       <c r="R50" t="n">
-        <v>6361174</v>
+        <v>6361187</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6206,12 +6207,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6222,10 +6223,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487394</v>
+        <v>120488904</v>
       </c>
       <c r="B51" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6234,41 +6235,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>694944</v>
+        <v>695053</v>
       </c>
       <c r="R51" t="n">
-        <v>6361275</v>
+        <v>6361123</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6312,12 +6322,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6328,7 +6338,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120488051</v>
+        <v>120487293</v>
       </c>
       <c r="B52" t="n">
         <v>86282</v>
@@ -6364,14 +6374,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694954</v>
+        <v>694983</v>
       </c>
       <c r="R52" t="n">
-        <v>6361151</v>
+        <v>6361234</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6418,12 +6428,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6434,10 +6444,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120484480</v>
+        <v>120487393</v>
       </c>
       <c r="B53" t="n">
-        <v>90356</v>
+        <v>86282</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6446,44 +6456,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brajdvät, Brajdvät, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>695044</v>
+        <v>694975</v>
       </c>
       <c r="R53" t="n">
-        <v>6360990</v>
+        <v>6361311</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6510,40 +6517,29 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6554,10 +6550,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120487043</v>
+        <v>120488051</v>
       </c>
       <c r="B54" t="n">
-        <v>97952</v>
+        <v>86282</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6570,34 +6566,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219862</v>
+        <v>3712</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694999</v>
+        <v>694954</v>
       </c>
       <c r="R54" t="n">
-        <v>6361192</v>
+        <v>6361151</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6644,12 +6640,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6660,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487031</v>
+        <v>120488053</v>
       </c>
       <c r="B55" t="n">
-        <v>86465</v>
+        <v>86282</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,38 +6668,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>694945</v>
+        <v>694983</v>
       </c>
       <c r="R55" t="n">
-        <v>6361314</v>
+        <v>6361108</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6738,6 +6734,11 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6750,12 +6751,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6766,10 +6767,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120488064</v>
+        <v>120487290</v>
       </c>
       <c r="B56" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6782,34 +6783,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>695059</v>
+        <v>694944</v>
       </c>
       <c r="R56" t="n">
-        <v>6361135</v>
+        <v>6361275</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6856,12 +6857,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6872,10 +6873,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120488052</v>
+        <v>120487363</v>
       </c>
       <c r="B57" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6884,38 +6885,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>694976</v>
+        <v>694940</v>
       </c>
       <c r="R57" t="n">
-        <v>6361129</v>
+        <v>6361207</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6962,12 +6963,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6978,10 +6979,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487292</v>
+        <v>120488894</v>
       </c>
       <c r="B58" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,37 +6995,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>694942</v>
+        <v>695063</v>
       </c>
       <c r="R58" t="n">
-        <v>6361278</v>
+        <v>6361108</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7054,11 +7064,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>många fruktkroppar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7073,12 +7078,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7089,10 +7094,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487295</v>
+        <v>120487275</v>
       </c>
       <c r="B59" t="n">
-        <v>86282</v>
+        <v>91272</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7105,21 +7110,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3712</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7129,10 +7134,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695000</v>
+        <v>695063</v>
       </c>
       <c r="R59" t="n">
-        <v>6361151</v>
+        <v>6361118</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7195,10 +7200,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487054</v>
+        <v>120487043</v>
       </c>
       <c r="B60" t="n">
-        <v>100194</v>
+        <v>97952</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7211,21 +7216,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7301,10 +7306,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120488049</v>
+        <v>120487060</v>
       </c>
       <c r="B61" t="n">
-        <v>86465</v>
+        <v>86302</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,38 +7318,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>694943</v>
+        <v>694955</v>
       </c>
       <c r="R61" t="n">
-        <v>6361165</v>
+        <v>6361273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7391,12 +7396,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7407,7 +7412,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120487293</v>
+        <v>120487277</v>
       </c>
       <c r="B62" t="n">
         <v>86282</v>
@@ -7447,10 +7452,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>694983</v>
+        <v>695004</v>
       </c>
       <c r="R62" t="n">
-        <v>6361234</v>
+        <v>6361020</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7513,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487059</v>
+        <v>120487411</v>
       </c>
       <c r="B63" t="n">
-        <v>86302</v>
+        <v>86414</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7525,38 +7530,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694945</v>
+        <v>694968</v>
       </c>
       <c r="R63" t="n">
-        <v>6361277</v>
+        <v>6361174</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7603,12 +7608,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7619,10 +7624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120487060</v>
+        <v>120488903</v>
       </c>
       <c r="B64" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7635,37 +7640,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>694955</v>
+        <v>694945</v>
       </c>
       <c r="R64" t="n">
-        <v>6361273</v>
+        <v>6361208</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7709,12 +7723,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7725,10 +7739,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120487046</v>
+        <v>120487295</v>
       </c>
       <c r="B65" t="n">
-        <v>86373</v>
+        <v>86282</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7737,25 +7751,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7765,10 +7779,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695003</v>
+        <v>695000</v>
       </c>
       <c r="R65" t="n">
-        <v>6361187</v>
+        <v>6361151</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7809,7 +7823,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7821,7 +7834,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7832,10 +7845,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120487363</v>
+        <v>120487031</v>
       </c>
       <c r="B66" t="n">
-        <v>86373</v>
+        <v>86465</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7844,38 +7857,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>694940</v>
+        <v>694945</v>
       </c>
       <c r="R66" t="n">
-        <v>6361207</v>
+        <v>6361314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7922,12 +7935,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7938,10 +7951,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120487048</v>
+        <v>120487412</v>
       </c>
       <c r="B67" t="n">
-        <v>86367</v>
+        <v>86414</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7950,20 +7963,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7974,14 +7987,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>694999</v>
+        <v>695014</v>
       </c>
       <c r="R67" t="n">
-        <v>6361192</v>
+        <v>6361123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8028,12 +8041,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8044,10 +8057,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120488894</v>
+        <v>120487034</v>
       </c>
       <c r="B68" t="n">
-        <v>90356</v>
+        <v>86282</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8056,50 +8069,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>695063</v>
+        <v>695029</v>
       </c>
       <c r="R68" t="n">
-        <v>6361108</v>
+        <v>6361151</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8143,12 +8147,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8159,10 +8163,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120488904</v>
+        <v>120484480</v>
       </c>
       <c r="B69" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8175,46 +8179,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Brajdvät, Brajdvät, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695053</v>
+        <v>695044</v>
       </c>
       <c r="R69" t="n">
-        <v>6361123</v>
+        <v>6360990</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8241,29 +8239,40 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8274,10 +8283,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120487332</v>
+        <v>120487294</v>
       </c>
       <c r="B70" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8286,25 +8295,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8314,10 +8323,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>694975</v>
+        <v>694937</v>
       </c>
       <c r="R70" t="n">
-        <v>6361311</v>
+        <v>6361266</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8380,10 +8389,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120488897</v>
+        <v>120487041</v>
       </c>
       <c r="B71" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8392,50 +8401,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695068</v>
+        <v>694996</v>
       </c>
       <c r="R71" t="n">
-        <v>6361100</v>
+        <v>6361187</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8479,12 +8479,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8495,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120505912</v>
+        <v>120504952</v>
       </c>
       <c r="B72" t="n">
-        <v>86282</v>
+        <v>90060</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8507,41 +8507,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>694995</v>
+        <v>694966</v>
       </c>
       <c r="R72" t="n">
-        <v>6360841</v>
+        <v>6360945</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8585,12 +8585,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8601,10 +8601,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120505895</v>
+        <v>120504950</v>
       </c>
       <c r="B73" t="n">
-        <v>86449</v>
+        <v>86367</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8613,41 +8613,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>694999</v>
+        <v>694965</v>
       </c>
       <c r="R73" t="n">
-        <v>6360873</v>
+        <v>6360935</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8691,12 +8691,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8707,10 +8707,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120505911</v>
+        <v>120504973</v>
       </c>
       <c r="B74" t="n">
-        <v>86282</v>
+        <v>86414</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8723,37 +8723,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>694994</v>
+        <v>695009</v>
       </c>
       <c r="R74" t="n">
-        <v>6361015</v>
+        <v>6360934</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8797,12 +8797,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8813,10 +8813,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120504952</v>
+        <v>120505895</v>
       </c>
       <c r="B75" t="n">
-        <v>90060</v>
+        <v>86449</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8829,37 +8829,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>694966</v>
+        <v>694999</v>
       </c>
       <c r="R75" t="n">
-        <v>6360945</v>
+        <v>6360873</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8903,12 +8903,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9025,7 +9025,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120504956</v>
+        <v>120505913</v>
       </c>
       <c r="B77" t="n">
         <v>86282</v>
@@ -9061,17 +9061,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695031</v>
+        <v>694996</v>
       </c>
       <c r="R77" t="n">
-        <v>6360930</v>
+        <v>6360879</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9109,19 +9109,18 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9238,7 +9237,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120504972</v>
+        <v>120504974</v>
       </c>
       <c r="B79" t="n">
         <v>86414</v>
@@ -9278,10 +9277,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>694900</v>
+        <v>695028</v>
       </c>
       <c r="R79" t="n">
-        <v>6360951</v>
+        <v>6360934</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9344,10 +9343,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120504950</v>
+        <v>120504972</v>
       </c>
       <c r="B80" t="n">
-        <v>86367</v>
+        <v>86414</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9356,20 +9355,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9384,10 +9383,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>694965</v>
+        <v>694900</v>
       </c>
       <c r="R80" t="n">
-        <v>6360935</v>
+        <v>6360951</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9450,7 +9449,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120505913</v>
+        <v>120504956</v>
       </c>
       <c r="B81" t="n">
         <v>86282</v>
@@ -9486,17 +9485,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>694996</v>
+        <v>695031</v>
       </c>
       <c r="R81" t="n">
-        <v>6360879</v>
+        <v>6360930</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9534,18 +9533,19 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9556,10 +9556,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120504973</v>
+        <v>120505911</v>
       </c>
       <c r="B82" t="n">
-        <v>86414</v>
+        <v>86282</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9572,37 +9572,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695009</v>
+        <v>694994</v>
       </c>
       <c r="R82" t="n">
-        <v>6360934</v>
+        <v>6361015</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9646,12 +9646,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9662,10 +9662,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120504974</v>
+        <v>120505912</v>
       </c>
       <c r="B83" t="n">
-        <v>86414</v>
+        <v>86282</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9678,37 +9678,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695028</v>
+        <v>694995</v>
       </c>
       <c r="R83" t="n">
-        <v>6360934</v>
+        <v>6360841</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9752,12 +9752,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4282,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487046</v>
+        <v>120488893</v>
       </c>
       <c r="B33" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4298,37 +4298,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>695003</v>
+        <v>695054</v>
       </c>
       <c r="R33" t="n">
-        <v>6361187</v>
+        <v>6361115</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4366,19 +4375,18 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4389,10 +4397,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487289</v>
+        <v>120488049</v>
       </c>
       <c r="B34" t="n">
-        <v>86302</v>
+        <v>86465</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4401,38 +4409,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>694955</v>
+        <v>694943</v>
       </c>
       <c r="R34" t="n">
-        <v>6361282</v>
+        <v>6361165</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4479,12 +4487,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4601,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120487395</v>
+        <v>120487060</v>
       </c>
       <c r="B36" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4613,38 +4621,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>694976</v>
+        <v>694955</v>
       </c>
       <c r="R36" t="n">
-        <v>6361175</v>
+        <v>6361273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4691,12 +4699,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4707,10 +4715,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487292</v>
+        <v>120487395</v>
       </c>
       <c r="B37" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4719,25 +4727,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4747,10 +4755,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>694942</v>
+        <v>694976</v>
       </c>
       <c r="R37" t="n">
-        <v>6361278</v>
+        <v>6361175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4783,11 +4791,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>många fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4818,10 +4821,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120487332</v>
+        <v>120487294</v>
       </c>
       <c r="B38" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4830,25 +4833,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4858,10 +4861,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>694975</v>
+        <v>694937</v>
       </c>
       <c r="R38" t="n">
-        <v>6361311</v>
+        <v>6361266</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4924,10 +4927,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120487059</v>
+        <v>120487031</v>
       </c>
       <c r="B39" t="n">
-        <v>86302</v>
+        <v>86465</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4936,25 +4939,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4967,7 +4970,7 @@
         <v>694945</v>
       </c>
       <c r="R39" t="n">
-        <v>6361277</v>
+        <v>6361314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5030,10 +5033,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487048</v>
+        <v>120487363</v>
       </c>
       <c r="B40" t="n">
-        <v>86367</v>
+        <v>86373</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,34 +5049,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>694999</v>
+        <v>694940</v>
       </c>
       <c r="R40" t="n">
-        <v>6361192</v>
+        <v>6361207</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5120,12 +5123,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5136,10 +5139,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487394</v>
+        <v>120488897</v>
       </c>
       <c r="B41" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5148,41 +5151,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694944</v>
+        <v>695068</v>
       </c>
       <c r="R41" t="n">
-        <v>6361275</v>
+        <v>6361100</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5226,12 +5238,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5242,10 +5254,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120488067</v>
+        <v>120484480</v>
       </c>
       <c r="B42" t="n">
-        <v>86414</v>
+        <v>90356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5254,41 +5266,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Brajdvät, Brajdvät, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>694971</v>
+        <v>695044</v>
       </c>
       <c r="R42" t="n">
-        <v>6361169</v>
+        <v>6360990</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5315,29 +5330,40 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5348,10 +5374,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120488893</v>
+        <v>120487049</v>
       </c>
       <c r="B43" t="n">
-        <v>90356</v>
+        <v>86367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,46 +5390,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695054</v>
+        <v>694996</v>
       </c>
       <c r="R43" t="n">
-        <v>6361115</v>
+        <v>6361187</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5447,12 +5464,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5463,10 +5480,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120488052</v>
+        <v>120487275</v>
       </c>
       <c r="B44" t="n">
-        <v>86282</v>
+        <v>91272</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5479,34 +5496,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3712</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>694976</v>
+        <v>695063</v>
       </c>
       <c r="R44" t="n">
-        <v>6361129</v>
+        <v>6361118</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5553,12 +5570,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5569,10 +5586,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120488049</v>
+        <v>120488052</v>
       </c>
       <c r="B45" t="n">
-        <v>86465</v>
+        <v>86282</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5581,25 +5598,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5609,10 +5626,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>694943</v>
+        <v>694976</v>
       </c>
       <c r="R45" t="n">
-        <v>6361165</v>
+        <v>6361129</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5675,10 +5692,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487032</v>
+        <v>120487295</v>
       </c>
       <c r="B46" t="n">
-        <v>86465</v>
+        <v>86282</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5687,25 +5704,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5715,10 +5732,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695026</v>
+        <v>695000</v>
       </c>
       <c r="R46" t="n">
-        <v>6361133</v>
+        <v>6361151</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5770,7 +5787,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5781,10 +5798,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120488905</v>
+        <v>120487289</v>
       </c>
       <c r="B47" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5797,46 +5814,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695053</v>
+        <v>694955</v>
       </c>
       <c r="R47" t="n">
-        <v>6361117</v>
+        <v>6361282</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5880,12 +5888,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5896,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120488897</v>
+        <v>120487043</v>
       </c>
       <c r="B48" t="n">
-        <v>86302</v>
+        <v>97952</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5908,50 +5916,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>219862</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695068</v>
+        <v>694999</v>
       </c>
       <c r="R48" t="n">
-        <v>6361100</v>
+        <v>6361192</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5995,12 +5994,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6117,10 +6116,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487049</v>
+        <v>120487332</v>
       </c>
       <c r="B50" t="n">
-        <v>86367</v>
+        <v>86449</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6129,38 +6128,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694996</v>
+        <v>694975</v>
       </c>
       <c r="R50" t="n">
-        <v>6361187</v>
+        <v>6361311</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6207,12 +6206,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6223,10 +6222,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120488904</v>
+        <v>120487393</v>
       </c>
       <c r="B51" t="n">
-        <v>86373</v>
+        <v>86282</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6235,50 +6234,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>695053</v>
+        <v>694975</v>
       </c>
       <c r="R51" t="n">
-        <v>6361123</v>
+        <v>6361311</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6322,12 +6312,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6338,10 +6328,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487293</v>
+        <v>120488903</v>
       </c>
       <c r="B52" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6350,41 +6340,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694983</v>
+        <v>694945</v>
       </c>
       <c r="R52" t="n">
-        <v>6361234</v>
+        <v>6361208</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6428,12 +6427,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6444,7 +6443,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487393</v>
+        <v>120487293</v>
       </c>
       <c r="B53" t="n">
         <v>86282</v>
@@ -6480,14 +6479,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>694975</v>
+        <v>694983</v>
       </c>
       <c r="R53" t="n">
-        <v>6361311</v>
+        <v>6361234</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6534,12 +6533,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6550,7 +6549,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120488051</v>
+        <v>120488053</v>
       </c>
       <c r="B54" t="n">
         <v>86282</v>
@@ -6590,10 +6589,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694954</v>
+        <v>694983</v>
       </c>
       <c r="R54" t="n">
-        <v>6361151</v>
+        <v>6361108</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6626,6 +6625,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6656,10 +6660,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120488053</v>
+        <v>120487059</v>
       </c>
       <c r="B55" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6668,38 +6672,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>694983</v>
+        <v>694945</v>
       </c>
       <c r="R55" t="n">
-        <v>6361108</v>
+        <v>6361277</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6734,11 +6738,6 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6751,12 +6750,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6873,10 +6872,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487363</v>
+        <v>120487292</v>
       </c>
       <c r="B57" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6889,21 +6888,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6913,10 +6912,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>694940</v>
+        <v>694942</v>
       </c>
       <c r="R57" t="n">
-        <v>6361207</v>
+        <v>6361278</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6949,6 +6948,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>många fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6979,10 +6983,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120488894</v>
+        <v>120487041</v>
       </c>
       <c r="B58" t="n">
-        <v>90356</v>
+        <v>86282</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6991,50 +6995,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>695063</v>
+        <v>694996</v>
       </c>
       <c r="R58" t="n">
-        <v>6361108</v>
+        <v>6361187</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7078,12 +7073,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7094,10 +7089,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487275</v>
+        <v>120487394</v>
       </c>
       <c r="B59" t="n">
-        <v>91272</v>
+        <v>86282</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7110,34 +7105,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>3712</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>695063</v>
+        <v>694944</v>
       </c>
       <c r="R59" t="n">
-        <v>6361118</v>
+        <v>6361275</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7184,12 +7179,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487043</v>
+        <v>120488905</v>
       </c>
       <c r="B60" t="n">
-        <v>97952</v>
+        <v>86373</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7212,41 +7207,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219862</v>
+        <v>248956</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>694999</v>
+        <v>695053</v>
       </c>
       <c r="R60" t="n">
-        <v>6361192</v>
+        <v>6361117</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7290,12 +7294,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7306,10 +7310,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120487060</v>
+        <v>120488894</v>
       </c>
       <c r="B61" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7322,37 +7326,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>694955</v>
+        <v>695063</v>
       </c>
       <c r="R61" t="n">
-        <v>6361273</v>
+        <v>6361108</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7396,12 +7409,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7518,7 +7531,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487411</v>
+        <v>120488067</v>
       </c>
       <c r="B63" t="n">
         <v>86414</v>
@@ -7554,14 +7567,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694968</v>
+        <v>694971</v>
       </c>
       <c r="R63" t="n">
-        <v>6361174</v>
+        <v>6361169</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7608,12 +7621,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7624,10 +7637,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120488903</v>
+        <v>120487412</v>
       </c>
       <c r="B64" t="n">
-        <v>86373</v>
+        <v>86414</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7636,50 +7649,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>694945</v>
+        <v>695014</v>
       </c>
       <c r="R64" t="n">
-        <v>6361208</v>
+        <v>6361123</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7723,12 +7727,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7739,10 +7743,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120487295</v>
+        <v>120487411</v>
       </c>
       <c r="B65" t="n">
-        <v>86282</v>
+        <v>86414</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7755,34 +7759,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>695000</v>
+        <v>694968</v>
       </c>
       <c r="R65" t="n">
-        <v>6361151</v>
+        <v>6361174</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7829,12 +7833,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7845,10 +7849,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120487031</v>
+        <v>120488051</v>
       </c>
       <c r="B66" t="n">
-        <v>86465</v>
+        <v>86282</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7857,38 +7861,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>694945</v>
+        <v>694954</v>
       </c>
       <c r="R66" t="n">
-        <v>6361314</v>
+        <v>6361151</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7935,12 +7939,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7951,10 +7955,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120487412</v>
+        <v>120487046</v>
       </c>
       <c r="B67" t="n">
-        <v>86414</v>
+        <v>86373</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7963,38 +7967,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>695014</v>
+        <v>695003</v>
       </c>
       <c r="R67" t="n">
-        <v>6361123</v>
+        <v>6361187</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8035,18 +8039,19 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8163,10 +8168,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120484480</v>
+        <v>120487048</v>
       </c>
       <c r="B69" t="n">
-        <v>90356</v>
+        <v>86367</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8179,40 +8184,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brajdvät, Brajdvät, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695044</v>
+        <v>694999</v>
       </c>
       <c r="R69" t="n">
-        <v>6360990</v>
+        <v>6361192</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8239,40 +8241,29 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:36</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8283,10 +8274,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120487294</v>
+        <v>120488904</v>
       </c>
       <c r="B70" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8299,37 +8290,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>694937</v>
+        <v>695053</v>
       </c>
       <c r="R70" t="n">
-        <v>6361266</v>
+        <v>6361123</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8373,12 +8373,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8389,10 +8389,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120487041</v>
+        <v>120487032</v>
       </c>
       <c r="B71" t="n">
-        <v>86282</v>
+        <v>86465</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8401,25 +8401,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>694996</v>
+        <v>695026</v>
       </c>
       <c r="R71" t="n">
-        <v>6361187</v>
+        <v>6361133</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8495,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120504952</v>
+        <v>120505912</v>
       </c>
       <c r="B72" t="n">
-        <v>90060</v>
+        <v>86282</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8507,41 +8507,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3286</v>
+        <v>3712</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>694966</v>
+        <v>694995</v>
       </c>
       <c r="R72" t="n">
-        <v>6360945</v>
+        <v>6360841</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8585,12 +8585,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8601,10 +8601,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120504950</v>
+        <v>120504974</v>
       </c>
       <c r="B73" t="n">
-        <v>86367</v>
+        <v>86414</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8613,20 +8613,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>694965</v>
+        <v>695028</v>
       </c>
       <c r="R73" t="n">
-        <v>6360935</v>
+        <v>6360934</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8707,10 +8707,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120504973</v>
+        <v>120505911</v>
       </c>
       <c r="B74" t="n">
-        <v>86414</v>
+        <v>86282</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8723,37 +8723,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695009</v>
+        <v>694994</v>
       </c>
       <c r="R74" t="n">
-        <v>6360934</v>
+        <v>6361015</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8797,12 +8797,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8813,10 +8813,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120505895</v>
+        <v>120504934</v>
       </c>
       <c r="B75" t="n">
-        <v>86449</v>
+        <v>86465</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8825,41 +8825,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>694999</v>
+        <v>695009</v>
       </c>
       <c r="R75" t="n">
-        <v>6360873</v>
+        <v>6360998</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8903,12 +8903,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8919,7 +8919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120504960</v>
+        <v>120505913</v>
       </c>
       <c r="B76" t="n">
         <v>86282</v>
@@ -8955,17 +8955,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>694902</v>
+        <v>694996</v>
       </c>
       <c r="R76" t="n">
-        <v>6360953</v>
+        <v>6360879</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9009,12 +9009,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120505913</v>
+        <v>120504952</v>
       </c>
       <c r="B77" t="n">
-        <v>86282</v>
+        <v>90060</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9037,41 +9037,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>694996</v>
+        <v>694966</v>
       </c>
       <c r="R77" t="n">
-        <v>6360879</v>
+        <v>6360945</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9115,12 +9115,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120504934</v>
+        <v>120504973</v>
       </c>
       <c r="B78" t="n">
-        <v>86465</v>
+        <v>86414</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9143,25 +9143,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9174,7 +9174,7 @@
         <v>695009</v>
       </c>
       <c r="R78" t="n">
-        <v>6360998</v>
+        <v>6360934</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120504974</v>
+        <v>120504950</v>
       </c>
       <c r="B79" t="n">
-        <v>86414</v>
+        <v>86367</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9249,20 +9249,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9277,10 +9277,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695028</v>
+        <v>694965</v>
       </c>
       <c r="R79" t="n">
-        <v>6360934</v>
+        <v>6360935</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9343,10 +9343,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120504972</v>
+        <v>120505895</v>
       </c>
       <c r="B80" t="n">
-        <v>86414</v>
+        <v>86449</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9355,41 +9355,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Öst om Däpps, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>694900</v>
+        <v>694999</v>
       </c>
       <c r="R80" t="n">
-        <v>6360951</v>
+        <v>6360873</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9433,12 +9433,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9449,10 +9449,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120504956</v>
+        <v>120504972</v>
       </c>
       <c r="B81" t="n">
-        <v>86282</v>
+        <v>86414</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9465,21 +9465,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695031</v>
+        <v>694900</v>
       </c>
       <c r="R81" t="n">
-        <v>6360930</v>
+        <v>6360951</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9533,7 +9533,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9556,7 +9555,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120505911</v>
+        <v>120504960</v>
       </c>
       <c r="B82" t="n">
         <v>86282</v>
@@ -9592,17 +9591,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>694994</v>
+        <v>694902</v>
       </c>
       <c r="R82" t="n">
-        <v>6361015</v>
+        <v>6360953</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9646,12 +9645,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9662,7 +9661,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120505912</v>
+        <v>120504956</v>
       </c>
       <c r="B83" t="n">
         <v>86282</v>
@@ -9698,17 +9697,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Öst om Däpps, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>694995</v>
+        <v>695031</v>
       </c>
       <c r="R83" t="n">
-        <v>6360841</v>
+        <v>6360930</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9746,18 +9745,19 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9765,6 +9765,1233 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120551345</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>695106</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6361828</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120551359</v>
+      </c>
+      <c r="B85" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>694985</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6361466</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120551401</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>695114</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6361880</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120551348</v>
+      </c>
+      <c r="B87" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>695081</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6361782</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120551350</v>
+      </c>
+      <c r="B88" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>695057</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6361723</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120551395</v>
+      </c>
+      <c r="B89" t="n">
+        <v>97905</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>695188</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6361865</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120551352</v>
+      </c>
+      <c r="B90" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>695042</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6361667</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120551349</v>
+      </c>
+      <c r="B91" t="n">
+        <v>109848</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>695057</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6361723</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>på ca 10 tallar</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120551356</v>
+      </c>
+      <c r="B92" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>695023</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6361602</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120551354</v>
+      </c>
+      <c r="B93" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>695038</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6361636</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120551343</v>
+      </c>
+      <c r="B94" t="n">
+        <v>110051</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sammetsbockrot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Pimpinella saxifraga subsp. nigra</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Mill.) Ces.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Domrörskog, Fröjel, Puser 1:30 (5)., Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>695106</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6361828</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53920-2023 artfynd.xlsx
+++ b/artfynd/A 53920-2023 artfynd.xlsx
@@ -6549,10 +6549,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120488053</v>
+        <v>120487059</v>
       </c>
       <c r="B54" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6561,38 +6561,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Klinte2, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694983</v>
+        <v>694945</v>
       </c>
       <c r="R54" t="n">
-        <v>6361108</v>
+        <v>6361277</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6627,11 +6627,6 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6644,12 +6639,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6660,10 +6655,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487059</v>
+        <v>120488053</v>
       </c>
       <c r="B55" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6672,38 +6667,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Klinte2, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>694945</v>
+        <v>694983</v>
       </c>
       <c r="R55" t="n">
-        <v>6361277</v>
+        <v>6361108</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6738,6 +6733,11 @@
           <t>2024-10-18</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6750,12 +6750,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
